--- a/Day-10/selected_students.xlsx
+++ b/Day-10/selected_students.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,19 @@
       </c>
       <c r="C4" t="n">
         <v>92</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
